--- a/results/cifar10_8_255_result.xlsx
+++ b/results/cifar10_8_255_result.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20380"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20382"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="14_{9487A2EE-8044-46AA-8320-98A7DC5C1309}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D23427D2-AF02-4968-AF04-C5AEF7CEB340}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{9487A2EE-8044-46AA-8320-98A7DC5C1309}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{50A4C5E3-0728-43AA-BBAC-DCE31D2AFF51}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>image</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -44,12 +44,6 @@
   <si>
     <t>BTime_NN</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>new_SR</t>
-  </si>
-  <si>
-    <t>new_NN</t>
   </si>
 </sst>
 </file>
@@ -374,14 +368,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="13.46484375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -400,14 +394,8 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>2</v>
       </c>
@@ -426,14 +414,8 @@
       <c r="F2">
         <v>15.539693355560299</v>
       </c>
-      <c r="G2">
-        <v>282.94</v>
-      </c>
-      <c r="H2">
-        <v>38.04</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>3</v>
       </c>
@@ -452,14 +434,8 @@
       <c r="F3">
         <v>41.46600866317749</v>
       </c>
-      <c r="G3">
-        <v>300.58999999999997</v>
-      </c>
-      <c r="H3">
-        <v>301.95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>5</v>
       </c>
@@ -478,14 +454,8 @@
       <c r="F4">
         <v>300.55661535263062</v>
       </c>
-      <c r="G4">
-        <v>302.24</v>
-      </c>
-      <c r="H4">
-        <v>300.68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>6</v>
       </c>
@@ -504,14 +474,8 @@
       <c r="F5">
         <v>300.30046248435968</v>
       </c>
-      <c r="G5">
-        <v>301.04000000000002</v>
-      </c>
-      <c r="H5">
-        <v>301.97000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>10</v>
       </c>
@@ -530,14 +494,8 @@
       <c r="F6">
         <v>2.0208816528320308</v>
       </c>
-      <c r="G6">
-        <v>5.92</v>
-      </c>
-      <c r="H6">
-        <v>8.23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>11</v>
       </c>
@@ -556,14 +514,8 @@
       <c r="F7">
         <v>5.2159173488616943</v>
       </c>
-      <c r="G7">
-        <v>300.92</v>
-      </c>
-      <c r="H7">
-        <v>301.82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>12</v>
       </c>
@@ -582,14 +534,8 @@
       <c r="F8">
         <v>18.671599626541141</v>
       </c>
-      <c r="G8">
-        <v>301.27999999999997</v>
-      </c>
-      <c r="H8">
-        <v>90.27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>14</v>
       </c>
@@ -608,14 +554,8 @@
       <c r="F9">
         <v>9.4270637035369873</v>
       </c>
-      <c r="G9">
-        <v>15.19</v>
-      </c>
-      <c r="H9">
-        <v>21.39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>15</v>
       </c>
@@ -634,14 +574,8 @@
       <c r="F10">
         <v>300.37138056755072</v>
       </c>
-      <c r="G10">
-        <v>300.54000000000002</v>
-      </c>
-      <c r="H10">
-        <v>300.23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>16</v>
       </c>
@@ -660,14 +594,8 @@
       <c r="F11">
         <v>302.30238962173462</v>
       </c>
-      <c r="G11">
-        <v>302.27</v>
-      </c>
-      <c r="H11">
-        <v>300.92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>17</v>
       </c>
@@ -686,14 +614,8 @@
       <c r="F12">
         <v>9.332965612411499</v>
       </c>
-      <c r="G12">
-        <v>8.0399999999999991</v>
-      </c>
-      <c r="H12">
-        <v>9.31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>19</v>
       </c>
@@ -712,14 +634,8 @@
       <c r="F13">
         <v>1.091900110244751</v>
       </c>
-      <c r="G13">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="H13">
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>20</v>
       </c>
@@ -738,14 +654,8 @@
       <c r="F14">
         <v>2.0245509147644039</v>
       </c>
-      <c r="G14">
-        <v>4.95</v>
-      </c>
-      <c r="H14">
-        <v>7.07</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>22</v>
       </c>
@@ -764,14 +674,8 @@
       <c r="F15">
         <v>1.091192960739136</v>
       </c>
-      <c r="G15">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="H15">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>24</v>
       </c>
@@ -790,14 +694,8 @@
       <c r="F16">
         <v>2.026633501052856</v>
       </c>
-      <c r="G16">
-        <v>1.96</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>29</v>
       </c>
@@ -816,14 +714,8 @@
       <c r="F17">
         <v>301.43746018409729</v>
       </c>
-      <c r="G17">
-        <v>302.01</v>
-      </c>
-      <c r="H17">
-        <v>301.11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>30</v>
       </c>
@@ -842,14 +734,8 @@
       <c r="F18">
         <v>15.90474271774292</v>
       </c>
-      <c r="G18">
-        <v>15.61</v>
-      </c>
-      <c r="H18">
-        <v>16.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>31</v>
       </c>
@@ -868,14 +754,8 @@
       <c r="F19">
         <v>2.0164840221405029</v>
       </c>
-      <c r="G19">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="H19">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>33</v>
       </c>
@@ -894,14 +774,8 @@
       <c r="F20">
         <v>46.939297437667847</v>
       </c>
-      <c r="G20">
-        <v>300.39</v>
-      </c>
-      <c r="H20">
-        <v>5.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>34</v>
       </c>
@@ -920,14 +794,8 @@
       <c r="F21">
         <v>2.0085947513580318</v>
       </c>
-      <c r="G21">
-        <v>3.93</v>
-      </c>
-      <c r="H21">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>35</v>
       </c>
@@ -946,14 +814,8 @@
       <c r="F22">
         <v>12.69560217857361</v>
       </c>
-      <c r="G22">
-        <v>21.53</v>
-      </c>
-      <c r="H22">
-        <v>12.54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>39</v>
       </c>
@@ -972,14 +834,8 @@
       <c r="F23">
         <v>301.91712760925287</v>
       </c>
-      <c r="G23">
-        <v>301.93</v>
-      </c>
-      <c r="H23">
-        <v>300.37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>40</v>
       </c>
@@ -998,14 +854,8 @@
       <c r="F24">
         <v>2.0165445804595952</v>
       </c>
-      <c r="G24">
-        <v>4.93</v>
-      </c>
-      <c r="H24">
-        <v>6.16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>42</v>
       </c>
@@ -1024,14 +874,8 @@
       <c r="F25">
         <v>1.096474409103394</v>
       </c>
-      <c r="G25">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="H25">
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>45</v>
       </c>
@@ -1050,14 +894,8 @@
       <c r="F26">
         <v>7.2446305751800537</v>
       </c>
-      <c r="G26">
-        <v>2.92</v>
-      </c>
-      <c r="H26">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>46</v>
       </c>
@@ -1076,14 +914,8 @@
       <c r="F27">
         <v>301.58523201942438</v>
       </c>
-      <c r="G27">
-        <v>301.89</v>
-      </c>
-      <c r="H27">
-        <v>301.07</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>50</v>
       </c>
@@ -1102,14 +934,8 @@
       <c r="F28">
         <v>16.87863397598267</v>
       </c>
-      <c r="G28">
-        <v>302.16000000000003</v>
-      </c>
-      <c r="H28">
-        <v>18.059999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>51</v>
       </c>
@@ -1128,14 +954,8 @@
       <c r="F29">
         <v>7.4997591972351074</v>
       </c>
-      <c r="G29">
-        <v>7.9</v>
-      </c>
-      <c r="H29">
-        <v>9.34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>52</v>
       </c>
@@ -1154,14 +974,8 @@
       <c r="F30">
         <v>300.84754300117493</v>
       </c>
-      <c r="G30">
-        <v>300.44</v>
-      </c>
-      <c r="H30">
-        <v>302.08</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>55</v>
       </c>
@@ -1180,14 +994,8 @@
       <c r="F31">
         <v>11.832792997360229</v>
       </c>
-      <c r="G31">
-        <v>16.05</v>
-      </c>
-      <c r="H31">
-        <v>16.190000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>56</v>
       </c>
@@ -1206,14 +1014,8 @@
       <c r="F32">
         <v>22.332391738891602</v>
       </c>
-      <c r="G32">
-        <v>300.66000000000003</v>
-      </c>
-      <c r="H32">
-        <v>111.11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>61</v>
       </c>
@@ -1232,14 +1034,8 @@
       <c r="F33">
         <v>2.003189325332642</v>
       </c>
-      <c r="G33">
-        <v>2.94</v>
-      </c>
-      <c r="H33">
-        <v>6.12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>65</v>
       </c>
@@ -1258,14 +1054,8 @@
       <c r="F34">
         <v>301.18067598342901</v>
       </c>
-      <c r="G34">
-        <v>301.70999999999998</v>
-      </c>
-      <c r="H34">
-        <v>302.07</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>67</v>
       </c>
@@ -1284,14 +1074,8 @@
       <c r="F35">
         <v>52.867683410644531</v>
       </c>
-      <c r="G35">
-        <v>302.11</v>
-      </c>
-      <c r="H35">
-        <v>301.91000000000003</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>68</v>
       </c>
@@ -1310,14 +1094,8 @@
       <c r="F36">
         <v>2.003849983215332</v>
       </c>
-      <c r="G36">
-        <v>1.96</v>
-      </c>
-      <c r="H36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>72</v>
       </c>
@@ -1336,14 +1114,8 @@
       <c r="F37">
         <v>10.51529693603516</v>
       </c>
-      <c r="G37">
-        <v>300.32</v>
-      </c>
-      <c r="H37">
-        <v>300.86</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>73</v>
       </c>
@@ -1362,14 +1134,8 @@
       <c r="F38">
         <v>301.43782782554632</v>
       </c>
-      <c r="G38">
-        <v>300.60000000000002</v>
-      </c>
-      <c r="H38">
-        <v>300.64999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>74</v>
       </c>
@@ -1388,14 +1154,8 @@
       <c r="F39">
         <v>301.35772442817688</v>
       </c>
-      <c r="G39">
-        <v>300.54000000000002</v>
-      </c>
-      <c r="H39">
-        <v>301.36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>75</v>
       </c>
@@ -1414,14 +1174,8 @@
       <c r="F40">
         <v>2.017360925674438</v>
       </c>
-      <c r="G40">
-        <v>2.92</v>
-      </c>
-      <c r="H40">
-        <v>4.0199999999999996</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>77</v>
       </c>
@@ -1440,14 +1194,8 @@
       <c r="F41">
         <v>300.77082085609442</v>
       </c>
-      <c r="G41">
-        <v>301.3</v>
-      </c>
-      <c r="H41">
-        <v>302.68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>80</v>
       </c>
@@ -1466,14 +1214,8 @@
       <c r="F42">
         <v>2.020983219146729</v>
       </c>
-      <c r="G42">
-        <v>2.23</v>
-      </c>
-      <c r="H42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>81</v>
       </c>
@@ -1492,14 +1234,8 @@
       <c r="F43">
         <v>302.01907134056091</v>
       </c>
-      <c r="G43">
-        <v>302.08999999999997</v>
-      </c>
-      <c r="H43">
-        <v>300.74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>82</v>
       </c>
@@ -1518,14 +1254,8 @@
       <c r="F44">
         <v>8.2122588157653809</v>
       </c>
-      <c r="G44">
-        <v>7.12</v>
-      </c>
-      <c r="H44">
-        <v>6.01</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>83</v>
       </c>
@@ -1544,14 +1274,8 @@
       <c r="F45">
         <v>9.309145450592041</v>
       </c>
-      <c r="G45">
-        <v>19.02</v>
-      </c>
-      <c r="H45">
-        <v>16.059999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>84</v>
       </c>
@@ -1570,14 +1294,8 @@
       <c r="F46">
         <v>2.008323192596436</v>
       </c>
-      <c r="G46">
-        <v>3.43</v>
-      </c>
-      <c r="H46">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>85</v>
       </c>
@@ -1596,14 +1314,8 @@
       <c r="F47">
         <v>302.07886123657232</v>
       </c>
-      <c r="G47">
-        <v>300.2</v>
-      </c>
-      <c r="H47">
-        <v>301.17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>87</v>
       </c>
@@ -1622,14 +1334,8 @@
       <c r="F48">
         <v>2.017783641815186</v>
       </c>
-      <c r="G48">
-        <v>5.93</v>
-      </c>
-      <c r="H48">
-        <v>6.12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>89</v>
       </c>
@@ -1648,14 +1354,8 @@
       <c r="F49">
         <v>22.747249603271481</v>
       </c>
-      <c r="G49">
-        <v>302.14</v>
-      </c>
-      <c r="H49">
-        <v>189.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>90</v>
       </c>
@@ -1674,14 +1374,8 @@
       <c r="F50">
         <v>10.763350486755369</v>
       </c>
-      <c r="G50">
-        <v>300.55</v>
-      </c>
-      <c r="H50">
-        <v>14.81</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>91</v>
       </c>
@@ -1700,14 +1394,8 @@
       <c r="F51">
         <v>2.0015935897827148</v>
       </c>
-      <c r="G51">
-        <v>8.69</v>
-      </c>
-      <c r="H51">
-        <v>9.35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>93</v>
       </c>
@@ -1726,14 +1414,8 @@
       <c r="F52">
         <v>1.0863761901855471</v>
       </c>
-      <c r="G52">
-        <v>1.08</v>
-      </c>
-      <c r="H52">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>96</v>
       </c>
@@ -1752,14 +1434,8 @@
       <c r="F53">
         <v>2.0559768676757808</v>
       </c>
-      <c r="G53">
-        <v>5.94</v>
-      </c>
-      <c r="H53">
-        <v>8.16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>97</v>
       </c>
@@ -1778,14 +1454,8 @@
       <c r="F54">
         <v>5.1671288013458252</v>
       </c>
-      <c r="G54">
-        <v>300.22000000000003</v>
-      </c>
-      <c r="H54">
-        <v>302.3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>98</v>
       </c>
@@ -1804,14 +1474,8 @@
       <c r="F55">
         <v>6.2389934062957764</v>
       </c>
-      <c r="G55">
-        <v>301</v>
-      </c>
-      <c r="H55">
-        <v>5.16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>99</v>
       </c>
@@ -1830,14 +1494,8 @@
       <c r="F56">
         <v>1.082647323608398</v>
       </c>
-      <c r="G56">
-        <v>1.08</v>
-      </c>
-      <c r="H56">
-        <v>1.1100000000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>100</v>
       </c>
@@ -1855,12 +1513,6 @@
       </c>
       <c r="F57">
         <v>2.0068609714508061</v>
-      </c>
-      <c r="G57">
-        <v>3.43</v>
-      </c>
-      <c r="H57">
-        <v>4.01</v>
       </c>
     </row>
   </sheetData>
